--- a/excel-files/TAGUIG_PATEROS/PATEROS ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/TAGUIG_PATEROS/PATEROS ELEMENTARY SCHOOL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="196" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4333A3D9-CF98-47DA-A04D-65A6AC6E9F93}"/>
+  <xr:revisionPtr revIDLastSave="197" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FF3A217-D9A9-4785-B992-B24975CA2D8E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3633,7 +3633,9 @@
       <c r="D6" s="1">
         <v>314</v>
       </c>
-      <c r="E6" s="1"/>
+      <c r="E6" s="1">
+        <v>2025</v>
+      </c>
       <c r="F6" s="5" t="s">
         <v>9</v>
       </c>
